--- a/Data/Final/Constituencies.xlsx
+++ b/Data/Final/Constituencies.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PowerBI Dashboards\Election_Result_Analysis\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PowerBI Dashboards\Election_Result_Analysis\Data\Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143CC09E-D3CF-4E22-9E7D-E1B5F1797C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C752DC-1BCD-44B8-84B0-01319A8F0A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="3" xr2:uid="{66093C65-D592-43DE-B23E-FD3CBA3A6E05}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{66093C65-D592-43DE-B23E-FD3CBA3A6E05}"/>
   </bookViews>
   <sheets>
     <sheet name="State Wise Constituencies" sheetId="2" r:id="rId1"/>
-    <sheet name="State Details." sheetId="8" r:id="rId2"/>
+    <sheet name="State Details" sheetId="8" r:id="rId2"/>
     <sheet name="Constituency" sheetId="3" r:id="rId3"/>
     <sheet name="Img" sheetId="7" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId5"/>
@@ -8282,7 +8282,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0380A08A-B9EF-4BBE-AEC1-AE7837ADF4C3}">
-  <dimension ref="A1:H544"/>
+  <dimension ref="A1:H579"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="14"/>
@@ -22439,7 +22439,150 @@
         <v>75</v>
       </c>
     </row>
+    <row r="545" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G545" s="15"/>
+      <c r="H545" s="15"/>
+    </row>
+    <row r="546" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G546" s="15"/>
+      <c r="H546" s="15"/>
+    </row>
+    <row r="547" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G547" s="15"/>
+      <c r="H547" s="15"/>
+    </row>
+    <row r="548" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G548" s="15"/>
+      <c r="H548" s="15"/>
+    </row>
+    <row r="549" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G549" s="15"/>
+      <c r="H549" s="15"/>
+    </row>
+    <row r="550" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G550" s="15"/>
+      <c r="H550" s="15"/>
+    </row>
+    <row r="551" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G551" s="15"/>
+      <c r="H551" s="15"/>
+    </row>
+    <row r="552" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G552" s="15"/>
+      <c r="H552" s="15"/>
+    </row>
+    <row r="553" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G553" s="15"/>
+      <c r="H553" s="15"/>
+    </row>
+    <row r="554" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G554" s="15"/>
+      <c r="H554" s="15"/>
+    </row>
+    <row r="555" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G555" s="15"/>
+      <c r="H555" s="15"/>
+    </row>
+    <row r="556" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G556" s="15"/>
+      <c r="H556" s="15"/>
+    </row>
+    <row r="557" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G557" s="15"/>
+      <c r="H557" s="15"/>
+    </row>
+    <row r="558" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G558" s="15"/>
+      <c r="H558" s="15"/>
+    </row>
+    <row r="559" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G559" s="15"/>
+      <c r="H559" s="15"/>
+    </row>
+    <row r="560" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G560" s="15"/>
+      <c r="H560" s="15"/>
+    </row>
+    <row r="561" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G561" s="15"/>
+      <c r="H561" s="15"/>
+    </row>
+    <row r="562" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G562" s="15"/>
+      <c r="H562" s="15"/>
+    </row>
+    <row r="563" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G563" s="15"/>
+      <c r="H563" s="15"/>
+    </row>
+    <row r="564" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G564" s="15"/>
+      <c r="H564" s="15"/>
+    </row>
+    <row r="565" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G565" s="15"/>
+      <c r="H565" s="15"/>
+    </row>
+    <row r="566" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G566" s="15"/>
+      <c r="H566" s="15"/>
+    </row>
+    <row r="567" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G567" s="15"/>
+      <c r="H567" s="15"/>
+    </row>
+    <row r="568" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G568" s="15"/>
+      <c r="H568" s="15"/>
+    </row>
+    <row r="569" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G569" s="15"/>
+      <c r="H569" s="15"/>
+    </row>
+    <row r="570" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G570" s="15"/>
+      <c r="H570" s="15"/>
+    </row>
+    <row r="571" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G571" s="15"/>
+      <c r="H571" s="15"/>
+    </row>
+    <row r="572" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G572" s="15"/>
+      <c r="H572" s="15"/>
+    </row>
+    <row r="573" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G573" s="15"/>
+      <c r="H573" s="15"/>
+    </row>
+    <row r="574" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G574" s="15"/>
+      <c r="H574" s="15"/>
+    </row>
+    <row r="575" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G575" s="15"/>
+      <c r="H575" s="15"/>
+    </row>
+    <row r="576" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G576" s="15"/>
+      <c r="H576" s="15"/>
+    </row>
+    <row r="577" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G577" s="15"/>
+      <c r="H577" s="15"/>
+    </row>
+    <row r="578" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G578" s="15"/>
+      <c r="H578" s="15"/>
+    </row>
+    <row r="579" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G579" s="15"/>
+      <c r="H579" s="15"/>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H579">
+    <sortCondition ref="A2:A579"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Data/Final/Constituencies.xlsx
+++ b/Data/Final/Constituencies.xlsx
@@ -8,21 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PowerBI Dashboards\Election_Result_Analysis\Data\Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C752DC-1BCD-44B8-84B0-01319A8F0A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D3375C9-E37A-4D2D-BDD4-AA3BC8AF6972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{66093C65-D592-43DE-B23E-FD3CBA3A6E05}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{66093C65-D592-43DE-B23E-FD3CBA3A6E05}"/>
   </bookViews>
   <sheets>
     <sheet name="State Wise Constituencies" sheetId="2" r:id="rId1"/>
     <sheet name="State Details" sheetId="8" r:id="rId2"/>
     <sheet name="Constituency" sheetId="3" r:id="rId3"/>
     <sheet name="Img" sheetId="7" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet name="Extra" sheetId="5" r:id="rId6"/>
+    <sheet name="Extra" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Img!$C$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet1!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'State Wise Constituencies'!$A$1:$J$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -23685,19 +23683,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D98FA4E6-6DAE-4E86-AD85-E3BBC2C095D2}">
-  <dimension ref="A8:A23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72F224D5-B003-49CF-B71B-3E86C4797FB3}">
   <dimension ref="A3:E41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Data/Final/Constituencies.xlsx
+++ b/Data/Final/Constituencies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PowerBI Dashboards\Election_Result_Analysis\Data\Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67413EDF-E422-412C-8A56-FDA5F3650BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2142A38-AC49-4C73-A05C-8C318CCCA81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="1" activeTab="1" xr2:uid="{66093C65-D592-43DE-B23E-FD3CBA3A6E05}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="516" activeTab="2" xr2:uid="{66093C65-D592-43DE-B23E-FD3CBA3A6E05}"/>
   </bookViews>
   <sheets>
     <sheet name="State Wise Constituencies" sheetId="2" r:id="rId1"/>
@@ -3913,18 +3913,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3941,7 +3935,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4035,7 +4029,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -20936,7 +20929,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0380A08A-B9EF-4BBE-AEC1-AE7837ADF4C3}">
-  <dimension ref="A1:L544"/>
+  <dimension ref="A1:H544"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="26.08984375" bestFit="1" customWidth="1"/>
@@ -20946,7 +20939,7 @@
     <col min="8" max="8" width="14.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
         <v>38</v>
       </c>
@@ -20972,7 +20965,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="14">
         <v>1</v>
       </c>
@@ -20998,7 +20991,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="14">
         <v>2</v>
       </c>
@@ -21024,7 +21017,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="14">
         <v>3</v>
       </c>
@@ -21050,7 +21043,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="14">
         <v>4</v>
       </c>
@@ -21076,7 +21069,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="14">
         <v>5</v>
       </c>
@@ -21102,7 +21095,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="14">
         <v>6</v>
       </c>
@@ -21127,14 +21120,8 @@
       <c r="H7" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="14">
         <v>7</v>
       </c>
@@ -21159,15 +21146,8 @@
       <c r="H8" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="K8">
-        <v>900</v>
-      </c>
-      <c r="L8" s="35">
-        <f>(L7*K8)/K7</f>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="14">
         <v>8</v>
       </c>
@@ -21193,7 +21173,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="14">
         <v>9</v>
       </c>
@@ -21219,7 +21199,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="14">
         <v>10</v>
       </c>
@@ -21245,7 +21225,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="14">
         <v>11</v>
       </c>
@@ -21271,7 +21251,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="14">
         <v>12</v>
       </c>
@@ -21297,7 +21277,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="14">
         <v>13</v>
       </c>
@@ -21323,7 +21303,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="14">
         <v>14</v>
       </c>
@@ -21349,7 +21329,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="14">
         <v>15</v>
       </c>

--- a/Data/Final/Constituencies.xlsx
+++ b/Data/Final/Constituencies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PowerBI Dashboards\Election_Result_Analysis\Data\Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2142A38-AC49-4C73-A05C-8C318CCCA81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADDB802-6488-4DAE-95E5-132631317BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="516" activeTab="2" xr2:uid="{66093C65-D592-43DE-B23E-FD3CBA3A6E05}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="516" activeTab="1" xr2:uid="{66093C65-D592-43DE-B23E-FD3CBA3A6E05}"/>
   </bookViews>
   <sheets>
     <sheet name="State Wise Constituencies" sheetId="2" r:id="rId1"/>
@@ -24,11 +24,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Constituency!$A$1:$H$544</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Img!$C$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'State Details'!$A$1:$X$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'State Wise Constituencies'!$A$1:$J$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3907" uniqueCount="1259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3907" uniqueCount="1260">
   <si>
     <t>https://en.wikipedia.org/wiki/List_of_constituencies_of_the_Lok_Sabha#/media/File:Andamanen_&amp;_Nikobaren_Wahlkreise_Lok_Sabha.svg</t>
   </si>
@@ -3844,6 +3845,9 @@
   </si>
   <si>
     <t>Aurangabad (MH)</t>
+  </si>
+  <si>
+    <t>UT</t>
   </si>
 </sst>
 </file>
@@ -10070,7 +10074,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{25865BF5-732B-4E4D-A326-563CB2856C73}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{25865BF5-732B-4E4D-A326-563CB2856C73}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B547" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0"/>
@@ -13798,6 +13802,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F0E535D-8A4B-441B-B944-FE52ED41D1C9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:X37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -13908,7 +13913,7 @@
         <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>623</v>
+        <v>1259</v>
       </c>
       <c r="D2" t="s">
         <v>1232</v>
@@ -13974,7 +13979,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -14048,7 +14053,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -14122,7 +14127,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -14196,7 +14201,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -14278,7 +14283,7 @@
         <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>623</v>
+        <v>1259</v>
       </c>
       <c r="D7" t="s">
         <v>1208</v>
@@ -14344,7 +14349,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -14426,7 +14431,7 @@
         <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>623</v>
+        <v>1259</v>
       </c>
       <c r="D9" t="s">
         <v>1199</v>
@@ -14482,7 +14487,7 @@
         <v>229</v>
       </c>
       <c r="C10" t="s">
-        <v>623</v>
+        <v>1259</v>
       </c>
       <c r="D10" t="s">
         <v>1197</v>
@@ -14548,7 +14553,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -14622,7 +14627,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -14696,7 +14701,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -14770,7 +14775,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -14852,7 +14857,7 @@
         <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>623</v>
+        <v>1259</v>
       </c>
       <c r="D15" t="s">
         <v>1164</v>
@@ -14918,7 +14923,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -14992,7 +14997,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -15066,7 +15071,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -15148,7 +15153,7 @@
         <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>623</v>
+        <v>1259</v>
       </c>
       <c r="D19" t="s">
         <v>1138</v>
@@ -15222,7 +15227,7 @@
         <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>623</v>
+        <v>1259</v>
       </c>
       <c r="D20" t="s">
         <v>1128</v>
@@ -15288,7 +15293,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -15362,7 +15367,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -15436,7 +15441,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -15510,7 +15515,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -15584,7 +15589,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -15658,7 +15663,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -15732,7 +15737,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -15814,7 +15819,7 @@
         <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>623</v>
+        <v>1259</v>
       </c>
       <c r="D28" t="s">
         <v>1069</v>
@@ -15880,7 +15885,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -15954,7 +15959,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -16028,7 +16033,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -16102,7 +16107,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -16176,7 +16181,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -16250,7 +16255,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -16324,7 +16329,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -16398,7 +16403,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -16472,7 +16477,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -16547,6 +16552,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:X37" xr:uid="{7F0E535D-8A4B-441B-B944-FE52ED41D1C9}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Union territory"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Data/Final/Constituencies.xlsx
+++ b/Data/Final/Constituencies.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADDB802-6488-4DAE-95E5-132631317BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="516" activeTab="1" xr2:uid="{66093C65-D592-43DE-B23E-FD3CBA3A6E05}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="516" xr2:uid="{66093C65-D592-43DE-B23E-FD3CBA3A6E05}"/>
   </bookViews>
   <sheets>
     <sheet name="State Wise Constituencies" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId8"/>
+    <pivotCache cacheId="20" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -10074,7 +10074,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{25865BF5-732B-4E4D-A326-563CB2856C73}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{25865BF5-732B-4E4D-A326-563CB2856C73}" name="PivotTable1" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B547" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0"/>
